--- a/docs/dnp3_template.xlsx
+++ b/docs/dnp3_template.xlsx
@@ -5928,7 +5928,10 @@
       <formula>AND(LEN(R5)=0,$Q5=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations count="9">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$A$2:$A$3</formula1>
+    </dataValidation>
     <dataValidation sqref="G5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 1 and 10." type="whole">
       <formula1>1</formula1>
       <formula2>10</formula2>
@@ -5936,6 +5939,12 @@
     <dataValidation sqref="H5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and 300." type="decimal">
       <formula1>0</formula1>
       <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="I5 Q5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$B$2:$B$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="J5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$AH$2:$AH$4</formula1>
     </dataValidation>
     <dataValidation sqref="K5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and +∞." type="decimal">
       <formula1>0</formula1>
@@ -6303,7 +6312,10 @@
       <formula>LEN(TRIM(P5))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations count="9">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$A$2:$A$3</formula1>
+    </dataValidation>
     <dataValidation sqref="G5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 1 and 10." type="whole">
       <formula1>1</formula1>
       <formula2>10</formula2>
@@ -6311,6 +6323,12 @@
     <dataValidation sqref="H5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and 300." type="decimal">
       <formula1>0</formula1>
       <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="I5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$B$2:$B$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="J5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$AH$2:$AH$4</formula1>
     </dataValidation>
     <dataValidation sqref="K5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and +∞." type="decimal">
       <formula1>0</formula1>
@@ -6475,14 +6493,20 @@
       <formula>AND(LEN(G5)=0,NOT($E5="TRUE"))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 1 and 86400." type="decimal">
       <formula1>1</formula1>
       <formula2>86400</formula2>
     </dataValidation>
+    <dataValidation sqref="C5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$AI$2:$AI$21</formula1>
+    </dataValidation>
     <dataValidation sqref="D5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and 15." type="whole">
       <formula1>0</formula1>
       <formula2>15</formula2>
+    </dataValidation>
+    <dataValidation sqref="E5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$B$2:$B$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7182,20 +7206,53 @@
       <formula>AND(LEN(AK5)=0,OR($R5 = "Write", $R5 = "ReadWrite", LEN($R5) = 0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="15">
+    <dataValidation sqref="B5 Y5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$A$2:$A$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$E$2:$E$47</formula1>
+    </dataValidation>
+    <dataValidation sqref="O5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$H$2:$H$46</formula1>
+    </dataValidation>
+    <dataValidation sqref="P5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$J$2:$J$17</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$K$2:$K$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="R5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$L$2:$L$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AB5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$CR$2:$CR$2</formula1>
+    </dataValidation>
     <dataValidation sqref="AC5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and 600." type="decimal">
       <formula1>0</formula1>
       <formula2>600</formula2>
+    </dataValidation>
+    <dataValidation sqref="AD5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$CS$2:$CS$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AE5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$CT$2:$CT$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AG5 AH5 AN5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$B$2:$B$3</formula1>
     </dataValidation>
     <dataValidation sqref="AI5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 1 and 60." type="decimal">
       <formula1>1</formula1>
       <formula2>60</formula2>
     </dataValidation>
+    <dataValidation sqref="AJ5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$AK$2:$AK$3</formula1>
+    </dataValidation>
     <dataValidation sqref="AO5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 1 and 100." type="whole">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation sqref="AP5:AQ5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 1 and 300." type="decimal">
+    <dataValidation sqref="AP5 AQ5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 1 and 300." type="decimal">
       <formula1>1</formula1>
       <formula2>300</formula2>
     </dataValidation>
@@ -8148,7 +8205,31 @@
       <formula>AND(LEN(AY5)=0,OR($S5 = "Write", $S5 = "ReadWrite", LEN($S5) = 0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="7">
+  <dataValidations count="20">
+    <dataValidation sqref="B5 AL5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$A$2:$A$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$E$2:$E$47</formula1>
+    </dataValidation>
+    <dataValidation sqref="O5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$M$2:$M$49</formula1>
+    </dataValidation>
+    <dataValidation sqref="P5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$J$2:$J$17</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$N$2:$N$76</formula1>
+    </dataValidation>
+    <dataValidation sqref="R5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$K$2:$K$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="S5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$L$2:$L$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="U5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$O$2:$O$4</formula1>
+    </dataValidation>
     <dataValidation sqref="Y5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between -1 and 100." type="decimal">
       <formula1>-1</formula1>
       <formula2>100</formula2>
@@ -8161,17 +8242,32 @@
       <formula1>30</formula1>
       <formula2>3600</formula2>
     </dataValidation>
+    <dataValidation sqref="AO5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$CU$2:$CU$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AR5 AW5 AZ5 BB5 BC5 BD5 BH5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$B$2:$B$3</formula1>
+    </dataValidation>
     <dataValidation sqref="AS5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and 600." type="decimal">
       <formula1>0</formula1>
       <formula2>600</formula2>
+    </dataValidation>
+    <dataValidation sqref="AT5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$CV$2:$CV$4</formula1>
     </dataValidation>
     <dataValidation sqref="AU5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and +∞." type="decimal">
       <formula1>0</formula1>
       <formula2>NaN</formula2>
     </dataValidation>
+    <dataValidation sqref="AX5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$AM$2:$AM$6</formula1>
+    </dataValidation>
     <dataValidation sqref="BA5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and +∞." type="whole">
       <formula1>0</formula1>
       <formula2>NaN</formula2>
+    </dataValidation>
+    <dataValidation sqref="BE5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$AD$2:$AD$4</formula1>
     </dataValidation>
     <dataValidation sqref="BI5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and 1." type="decimal">
       <formula1>0</formula1>
@@ -8935,18 +9031,51 @@
       <formula>AND(LEN(AI5)=0,OR($R5 = "Read", $R5 = "ReadWrite", LEN($R5) = 0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="15">
+    <dataValidation sqref="B5 Y5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$A$2:$A$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$CZ$2:$CZ$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="O5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$H$2:$H$46</formula1>
+    </dataValidation>
+    <dataValidation sqref="P5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$J$2:$J$17</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$K$2:$K$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="R5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$CX$2:$CX$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="AB5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$CW$2:$CW$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AE5 AJ5 AM5 AO5 AP5 AQ5 AU5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$B$2:$B$3</formula1>
+    </dataValidation>
     <dataValidation sqref="AF5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and 600." type="decimal">
       <formula1>0</formula1>
       <formula2>600</formula2>
+    </dataValidation>
+    <dataValidation sqref="AG5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$CY$2:$CY$4</formula1>
     </dataValidation>
     <dataValidation sqref="AH5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and +∞." type="decimal">
       <formula1>0</formula1>
       <formula2>NaN</formula2>
     </dataValidation>
+    <dataValidation sqref="AK5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$AM$2:$AM$6</formula1>
+    </dataValidation>
     <dataValidation sqref="AN5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and +∞." type="whole">
       <formula1>0</formula1>
       <formula2>NaN</formula2>
+    </dataValidation>
+    <dataValidation sqref="AR5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$AD$2:$AD$4</formula1>
     </dataValidation>
     <dataValidation sqref="AV5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and 1." type="decimal">
       <formula1>0</formula1>
@@ -9063,6 +9192,14 @@
       <formula>LEN(TRIM(A5))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$A$2:$A$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
@@ -9175,6 +9312,14 @@
       <formula>LEN(TRIM(D5))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$FV$2:$FV$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
@@ -9349,7 +9494,10 @@
       <formula>LEN(TRIM(H5))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$A$2:$A$3</formula1>
+    </dataValidation>
     <dataValidation sqref="G5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 1 and 60." type="decimal">
       <formula1>1</formula1>
       <formula2>60</formula2>
@@ -9463,7 +9611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FV5"/>
+  <dimension ref="A1:FV279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="17.140625" customWidth="1" style="82" min="1" max="1"/>
@@ -9631,3328 +9779,8096 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="82">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>YesNo</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TrueFalse</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>AlarmEventCause</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AlarmSeverity</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MeasurementType</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>TagSemantics</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>DMSType</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>DiscreteSignalType</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>AbnormalState</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PhaseCode</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>WindingType</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>SignalDirection</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>AnalogSignalType</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>UnitSymbol</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>FlowDirection</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>RemoteUnitType</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>TimeZone</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>RedundancyBehaviorType</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>SOEGroup</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>ProtocolTypeConitel</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>ScanTypeConitel</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>OperateType</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>DiscreteInputTypeConitel</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>SectionConitel</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t xml:space="preserve">DiscreteOutputDataTypeConitel </t>
         </is>
       </c>
-      <c r="AA1" s="4" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>CommandTypeConitel</t>
         </is>
       </c>
-      <c r="AB1" s="4" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>FunctionCodeConitel</t>
         </is>
       </c>
-      <c r="AC1" s="4" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>AnalogInputTypeConitel</t>
         </is>
       </c>
-      <c r="AD1" s="4" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>DeadbandDataType</t>
         </is>
       </c>
-      <c r="AE1" s="4" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>DNP3Scan</t>
         </is>
       </c>
-      <c r="AF1" s="4" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>TimeSyncMode</t>
         </is>
       </c>
-      <c r="AG1" s="4" t="n"/>
-      <c r="AH1" s="4" t="inlineStr">
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr">
         <is>
           <t>DNP3ConfirmMode</t>
         </is>
       </c>
-      <c r="AI1" s="4" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>DNP3ObjectGroup</t>
         </is>
       </c>
-      <c r="AJ1" s="4" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>DNP3InputType</t>
         </is>
       </c>
-      <c r="AK1" s="4" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>DNP3OutputType</t>
         </is>
       </c>
-      <c r="AL1" s="4" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ControlCode</t>
         </is>
       </c>
-      <c r="AM1" s="4" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>DNP3Variation</t>
         </is>
       </c>
-      <c r="AN1" s="4" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>DNP3SlaveEvent</t>
         </is>
       </c>
-      <c r="AO1" s="4" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>DNP3SlaveDiscreteInputDataType</t>
         </is>
       </c>
-      <c r="AP1" s="4" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>DNP3SlaveClassData</t>
         </is>
       </c>
-      <c r="AQ1" s="4" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>DNP3SlaveAnalogInputDataType</t>
         </is>
       </c>
-      <c r="AR1" s="4" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>DNP3SlaveCounterDataType</t>
         </is>
       </c>
-      <c r="AS1" s="4" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>IccpVersion</t>
         </is>
       </c>
-      <c r="AT1" s="4" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>IccpBlocks</t>
         </is>
       </c>
-      <c r="AU1" s="4" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>ConnectionRole</t>
         </is>
       </c>
-      <c r="AV1" s="4" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>ServiceRole</t>
         </is>
       </c>
-      <c r="AW1" s="4" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>AuthenticationMode</t>
         </is>
       </c>
-      <c r="AX1" s="4" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>DstsType</t>
         </is>
       </c>
-      <c r="AY1" s="4" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>IccpScope</t>
         </is>
       </c>
-      <c r="AZ1" s="4" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>IccpDataValueType</t>
         </is>
       </c>
-      <c r="BA1" s="4" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>IECCounterInterrogationType</t>
         </is>
       </c>
-      <c r="BB1" s="4" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>IECClockSyncMode</t>
         </is>
       </c>
-      <c r="BC1" s="4" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>OctetSize</t>
         </is>
       </c>
-      <c r="BD1" s="4" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>IEC101LinkMode</t>
         </is>
       </c>
-      <c r="BE1" s="4" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>IEC101ConfirmMode</t>
         </is>
       </c>
-      <c r="BF1" s="4" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>ModemCallType</t>
         </is>
       </c>
-      <c r="BG1" s="4" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>ModemCommandType</t>
         </is>
       </c>
-      <c r="BH1" s="4" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>BaudRate</t>
         </is>
       </c>
-      <c r="BI1" s="4" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>IECDiscreteType</t>
         </is>
       </c>
-      <c r="BJ1" s="4" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>IECCommandQualifier</t>
         </is>
       </c>
-      <c r="BK1" s="4" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>CommandState</t>
         </is>
       </c>
-      <c r="BL1" s="4" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>IECAnalogType</t>
         </is>
       </c>
-      <c r="BM1" s="4" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>IECRateType</t>
         </is>
       </c>
-      <c r="BN1" s="4" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>ScanTypeMD3</t>
         </is>
       </c>
-      <c r="BO1" s="4" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>DiscreteInputModuleTypeMD3</t>
         </is>
       </c>
-      <c r="BP1" s="4" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>DiscreteInputDataTypeMD3</t>
         </is>
       </c>
-      <c r="BQ1" s="4" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>DiscreteOutputTypeMD3</t>
         </is>
       </c>
-      <c r="BR1" s="4" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t xml:space="preserve">DiscreteOutputDataTypeMD3 </t>
         </is>
       </c>
-      <c r="BS1" s="4" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>CmdTypeMD3</t>
         </is>
       </c>
-      <c r="BT1" s="4" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>AnalogInputModuleTypeMD3</t>
         </is>
       </c>
-      <c r="BU1" s="4" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>AnalogInputDataTypeMD3</t>
         </is>
       </c>
-      <c r="BV1" s="4" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>AnalogOutputTypeMD3</t>
         </is>
       </c>
-      <c r="BW1" s="4" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>ModbusByteOrder</t>
         </is>
       </c>
-      <c r="BX1" s="4" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>ModbusTransmissionMode</t>
         </is>
       </c>
-      <c r="BY1" s="4" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>ModbusRegisterType</t>
         </is>
       </c>
-      <c r="BZ1" s="4" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>ModbusDiscreteOutputType</t>
         </is>
       </c>
-      <c r="CA1" s="4" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>ModbusAnalogType</t>
         </is>
       </c>
-      <c r="CB1" s="4" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>SecurityCodeSeries5</t>
         </is>
       </c>
-      <c r="CC1" s="4" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>ScanTypeSeries5</t>
         </is>
       </c>
-      <c r="CD1" s="4" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>DiscreteTypeSeries5</t>
         </is>
       </c>
-      <c r="CE1" s="4" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>ScanTypeVanComm</t>
         </is>
       </c>
-      <c r="CF1" s="4" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>DiscreteInputTypeVanComm</t>
         </is>
       </c>
-      <c r="CG1" s="4" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>DiscreteOutputTypeVanComm</t>
         </is>
       </c>
-      <c r="CH1" s="4" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>AnalogTypeVanComm</t>
         </is>
       </c>
-      <c r="CI1" s="4" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>CalculationParamType</t>
         </is>
       </c>
-      <c r="CJ1" s="4" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t xml:space="preserve"> InputTriggerType</t>
         </is>
       </c>
-      <c r="CK1" s="4" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>RemoteUnitType</t>
         </is>
       </c>
-      <c r="CL1" s="4" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>OperateType</t>
         </is>
       </c>
-      <c r="CM1" s="4" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="CN1" s="4" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="CO1" s="4" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="CP1" s="4" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>SignalDirection</t>
         </is>
       </c>
-      <c r="CQ1" s="4" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>MeasurementType</t>
         </is>
       </c>
-      <c r="CR1" s="4" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="CS1" s="4" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>OperateType</t>
         </is>
       </c>
-      <c r="CT1" s="4" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>DNP3InputType</t>
         </is>
       </c>
-      <c r="CU1" s="4" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="CV1" s="4" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>OperateType</t>
         </is>
       </c>
-      <c r="CW1" s="4" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="CX1" s="4" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>SignalDirection</t>
         </is>
       </c>
-      <c r="CY1" s="4" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>OperateType</t>
         </is>
       </c>
-      <c r="CZ1" s="4" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>MeasurementType</t>
         </is>
       </c>
-      <c r="DA1" s="4" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="DB1" s="4" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>OperateType</t>
         </is>
       </c>
-      <c r="DC1" s="4" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="DD1" s="4" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>OperateType</t>
         </is>
       </c>
-      <c r="DE1" s="4" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>RemoteUnitType</t>
         </is>
       </c>
-      <c r="DF1" s="4" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>RemoteUnitType</t>
         </is>
       </c>
-      <c r="DG1" s="4" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="DH1" s="4" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>IccpDataValueType</t>
         </is>
       </c>
-      <c r="DI1" s="4" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="DJ1" s="4" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>IccpDataValueType</t>
         </is>
       </c>
-      <c r="DK1" s="4" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="DL1" s="4" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>SignalDirection</t>
         </is>
       </c>
-      <c r="DM1" s="4" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>IccpDataValueType</t>
         </is>
       </c>
-      <c r="DN1" s="4" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>MeasurementType</t>
         </is>
       </c>
-      <c r="DO1" s="4" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>IccpDataValueType</t>
         </is>
       </c>
-      <c r="DP1" s="4" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>IccpDataValueType</t>
         </is>
       </c>
-      <c r="DQ1" s="4" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>RemoteUnitType</t>
         </is>
       </c>
-      <c r="DR1" s="4" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>OctetSize</t>
         </is>
       </c>
-      <c r="DS1" s="4" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>OctetSize</t>
         </is>
       </c>
-      <c r="DT1" s="4" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>OctetSize</t>
         </is>
       </c>
-      <c r="DU1" s="4" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>OctetSize</t>
         </is>
       </c>
-      <c r="DV1" s="4" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>BaudRate</t>
         </is>
       </c>
-      <c r="DW1" s="4" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>OctetSize</t>
         </is>
       </c>
-      <c r="DX1" s="4" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="DY1" s="4" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>IECDiscreteType</t>
         </is>
       </c>
-      <c r="DZ1" s="4" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>IECDiscreteType</t>
         </is>
       </c>
-      <c r="EA1" s="4" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="EB1" s="4" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>IECAnalogType</t>
         </is>
       </c>
-      <c r="EC1" s="4" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="ED1" s="4" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>SignalDirection</t>
         </is>
       </c>
-      <c r="EE1" s="4" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>MeasurementType</t>
         </is>
       </c>
-      <c r="EF1" s="4" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>IECAnalogType</t>
         </is>
       </c>
-      <c r="EG1" s="4" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="EH1" s="4" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>IECDiscreteType</t>
         </is>
       </c>
-      <c r="EI1" s="4" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>IECDiscreteType</t>
         </is>
       </c>
-      <c r="EJ1" s="4" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="EK1" s="4" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>IECAnalogType</t>
         </is>
       </c>
-      <c r="EL1" s="4" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>RemoteUnitType</t>
         </is>
       </c>
-      <c r="EM1" s="4" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>OctetSize</t>
         </is>
       </c>
-      <c r="EN1" s="4" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>RemoteUnitType</t>
         </is>
       </c>
-      <c r="EO1" s="4" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="EP1" s="4" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>IECDiscreteType</t>
         </is>
       </c>
-      <c r="EQ1" s="4" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>IECDiscreteType</t>
         </is>
       </c>
-      <c r="ER1" s="4" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="ES1" s="4" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>IECAnalogType</t>
         </is>
       </c>
-      <c r="ET1" s="4" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>IECAnalogType</t>
         </is>
       </c>
-      <c r="EU1" s="4" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="EV1" s="4" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>SignalDirection</t>
         </is>
       </c>
-      <c r="EW1" s="4" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>IECAnalogType</t>
         </is>
       </c>
-      <c r="EX1" s="4" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>IECAnalogType</t>
         </is>
       </c>
-      <c r="EY1" s="4" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>MeasurementType</t>
         </is>
       </c>
-      <c r="EZ1" s="4" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="FA1" s="4" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="FB1" s="4" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="FC1" s="4" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>SignalDirection</t>
         </is>
       </c>
-      <c r="FD1" s="4" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>MeasurementType</t>
         </is>
       </c>
-      <c r="FE1" s="4" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="FF1" s="4" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="FG1" s="4" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>ModbusRegisterType</t>
         </is>
       </c>
-      <c r="FH1" s="4" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="FI1" s="4" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>SignalDirection</t>
         </is>
       </c>
-      <c r="FJ1" s="4" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>ModbusRegisterType</t>
         </is>
       </c>
-      <c r="FK1" s="4" t="inlineStr">
+      <c r="FK1" t="inlineStr">
         <is>
           <t>MeasurementType</t>
         </is>
       </c>
-      <c r="FL1" s="4" t="inlineStr">
+      <c r="FL1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="FM1" s="4" t="inlineStr">
+      <c r="FM1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="FN1" s="4" t="inlineStr">
+      <c r="FN1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="FO1" s="4" t="inlineStr">
+      <c r="FO1" t="inlineStr">
         <is>
           <t>SignalDirection</t>
         </is>
       </c>
-      <c r="FP1" s="4" t="inlineStr">
+      <c r="FP1" t="inlineStr">
         <is>
           <t>MeasurementType</t>
         </is>
       </c>
-      <c r="FQ1" s="4" t="inlineStr">
+      <c r="FQ1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="FR1" s="4" t="inlineStr">
+      <c r="FR1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="FS1" s="4" t="inlineStr">
+      <c r="FS1" t="inlineStr">
         <is>
           <t>RemotePointType</t>
         </is>
       </c>
-      <c r="FT1" s="4" t="inlineStr">
+      <c r="FT1" t="inlineStr">
         <is>
           <t>SignalDirection</t>
         </is>
       </c>
-      <c r="FU1" s="4" t="inlineStr">
+      <c r="FU1" t="inlineStr">
         <is>
           <t>MeasurementType</t>
         </is>
       </c>
-      <c r="FV1" s="4" t="inlineStr">
+      <c r="FV1" t="inlineStr">
         <is>
           <t>CalculationParamType</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" s="82">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>ApplicationAlarm</t>
         </is>
       </c>
-      <c r="D2" s="0" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Severidade 16</t>
         </is>
       </c>
-      <c r="E2" s="0" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Unitless</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>DoNotOperatorClose</t>
         </is>
       </c>
-      <c r="G2" s="0" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>SUBSTATION</t>
         </is>
       </c>
-      <c r="H2" s="0" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I2" s="0" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="J2" s="0" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K2" s="0" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L2" s="0" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="M2" s="0" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="N2" s="0" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="O2" s="0" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Undirected</t>
         </is>
       </c>
-      <c r="P2" s="0" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>RTU</t>
         </is>
       </c>
-      <c r="Q2" s="0" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>(UTC-12:00) International Date Line West</t>
         </is>
       </c>
-      <c r="R2" s="0" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>PrioritizeCostFactor</t>
         </is>
       </c>
-      <c r="S2" s="0" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Group07</t>
         </is>
       </c>
-      <c r="T2" s="0" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Conitel2025</t>
         </is>
       </c>
-      <c r="U2" s="0" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Scan</t>
         </is>
       </c>
-      <c r="V2" s="0" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="W2" s="0" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>DirectOperate</t>
         </is>
       </c>
-      <c r="X2" s="0" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SingleBit</t>
         </is>
       </c>
-      <c r="Y2" s="0" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>SectionA</t>
         </is>
       </c>
-      <c r="Z2" s="0" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>SingleCoord</t>
         </is>
       </c>
-      <c r="AA2" s="0" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>TripClose</t>
         </is>
       </c>
-      <c r="AB2" s="0" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Trip</t>
         </is>
       </c>
-      <c r="AC2" s="0" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>TwelveBitSignedMagnitude</t>
         </is>
       </c>
-      <c r="AD2" s="0" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Int32</t>
         </is>
       </c>
-      <c r="AE2" s="0" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Class0</t>
         </is>
       </c>
-      <c r="AF2" s="0" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="AG2" s="0" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AH2" s="0" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>Never</t>
         </is>
       </c>
-      <c r="AI2" s="0" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>BinaryInput</t>
         </is>
       </c>
-      <c r="AJ2" s="0" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>SingleBit</t>
         </is>
       </c>
-      <c r="AK2" s="0" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>SingleCoord</t>
         </is>
       </c>
-      <c r="AL2" s="0" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>Nul</t>
         </is>
       </c>
-      <c r="AM2" s="0" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="AN2" s="0" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>WithoutTime</t>
         </is>
       </c>
-      <c r="AO2" s="0" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>BinaryInputPackedFormat</t>
         </is>
       </c>
-      <c r="AP2" s="0" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>Class1</t>
         </is>
       </c>
-      <c r="AQ2" s="0" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>Int32WithFlag</t>
         </is>
       </c>
-      <c r="AR2" s="0" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>Int32WithFlag</t>
         </is>
       </c>
-      <c r="AS2" s="0" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>Version1996</t>
         </is>
       </c>
-      <c r="AT2" s="0" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>Block1</t>
         </is>
       </c>
-      <c r="AU2" s="0" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>Outgoing</t>
         </is>
       </c>
-      <c r="AV2" s="0" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="AW2" s="0" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AX2" s="0" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>ManualRBE</t>
         </is>
       </c>
-      <c r="AY2" s="0" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>Vcc</t>
         </is>
       </c>
-      <c r="AZ2" s="0" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="BA2" s="0" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>CounterRead</t>
         </is>
       </c>
-      <c r="BB2" s="0" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>SyncOnly</t>
         </is>
       </c>
-      <c r="BC2" s="0" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>OneOctet</t>
         </is>
       </c>
-      <c r="BD2" s="0" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>Unbalanced</t>
         </is>
       </c>
-      <c r="BE2" s="0" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>Sometimes</t>
         </is>
       </c>
-      <c r="BF2" s="0" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>DialOut</t>
         </is>
       </c>
-      <c r="BG2" s="0" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>BaudRate</t>
         </is>
       </c>
-      <c r="BH2" s="0" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>B100</t>
         </is>
       </c>
-      <c r="BI2" s="0" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>IECNone</t>
         </is>
       </c>
-      <c r="BJ2" s="0" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>UseDefault</t>
         </is>
       </c>
-      <c r="BK2" s="0" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>On</t>
         </is>
       </c>
-      <c r="BL2" s="0" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>IECShortNormalized</t>
         </is>
       </c>
-      <c r="BM2" s="0" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>IECRateTimestamp</t>
         </is>
       </c>
-      <c r="BN2" s="0" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>AnalogUnconditional</t>
         </is>
       </c>
-      <c r="BO2" s="0" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>DigitalInputModuleDCM</t>
         </is>
       </c>
-      <c r="BP2" s="0" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>SingleBit</t>
         </is>
       </c>
-      <c r="BQ2" s="0" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>RaiseLower</t>
         </is>
       </c>
-      <c r="BR2" s="0" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>SingleCoord</t>
         </is>
       </c>
-      <c r="BS2" s="0" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>Trip</t>
         </is>
       </c>
-      <c r="BT2" s="0" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>AnalogInputModule</t>
         </is>
       </c>
-      <c r="BU2" s="0" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>TwelveBitSignedMagnitude</t>
         </is>
       </c>
-      <c r="BV2" s="0" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>AOMType</t>
         </is>
       </c>
-      <c r="BW2" s="0" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>LittleEndian</t>
         </is>
       </c>
-      <c r="BX2" s="0" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>TCP</t>
         </is>
       </c>
-      <c r="BY2" s="0" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>Coil</t>
         </is>
       </c>
-      <c r="BZ2" s="0" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>SingleCoord</t>
         </is>
       </c>
-      <c r="CA2" s="0" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="CB2" s="0" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>LRC8bit</t>
         </is>
       </c>
-      <c r="CC2" s="0" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>ExceptionScan</t>
         </is>
       </c>
-      <c r="CD2" s="0" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>SingleCoord</t>
         </is>
       </c>
-      <c r="CE2" s="0" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>AnalogScan</t>
         </is>
       </c>
-      <c r="CF2" s="0" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>MomentaryStatus</t>
         </is>
       </c>
-      <c r="CG2" s="0" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>SingleCoord</t>
         </is>
       </c>
-      <c r="CH2" s="0" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="CI2" s="0" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>Bool</t>
         </is>
       </c>
-      <c r="CJ2" s="0" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="CK2" s="0" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>RTU</t>
         </is>
       </c>
-      <c r="CL2" s="0" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>DirectOperate</t>
         </is>
       </c>
-      <c r="CM2" s="0" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="CN2" s="0" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="CO2" s="0" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="CP2" s="0" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="CQ2" s="0" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>Discrete</t>
         </is>
       </c>
-      <c r="CR2" s="0" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="CS2" s="0" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>DirectOperate</t>
         </is>
       </c>
-      <c r="CT2" s="0" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>SingleBit</t>
         </is>
       </c>
-      <c r="CU2" s="0" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="CV2" s="0" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>DirectOperate</t>
         </is>
       </c>
-      <c r="CW2" s="0" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="CX2" s="0" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="CY2" s="0" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>DirectOperate</t>
         </is>
       </c>
-      <c r="CZ2" s="0" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>Discrete</t>
         </is>
       </c>
-      <c r="DA2" s="0" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="DB2" s="0" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>DirectOperate</t>
         </is>
       </c>
-      <c r="DC2" s="0" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="DD2" s="0" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>DirectOperate</t>
         </is>
       </c>
-      <c r="DE2" s="0" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>ControlCenter</t>
         </is>
       </c>
-      <c r="DF2" s="0" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>ControlCenter</t>
         </is>
       </c>
-      <c r="DG2" s="0" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="DH2" s="0" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="DI2" s="0" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="DJ2" s="0" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>Real</t>
         </is>
       </c>
-      <c r="DK2" s="0" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="DL2" s="0" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="DM2" s="0" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>Real</t>
         </is>
       </c>
-      <c r="DN2" s="0" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>Discrete</t>
         </is>
       </c>
-      <c r="DO2" s="0" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="DP2" s="0" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>Real</t>
         </is>
       </c>
-      <c r="DQ2" s="0" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>RTU</t>
         </is>
       </c>
-      <c r="DR2" s="0" t="inlineStr">
+      <c r="DR2" t="inlineStr">
         <is>
           <t>OneOctet</t>
         </is>
       </c>
-      <c r="DS2" s="0" t="inlineStr">
+      <c r="DS2" t="inlineStr">
         <is>
           <t>OneOctet</t>
         </is>
       </c>
-      <c r="DT2" s="0" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>OneOctet</t>
         </is>
       </c>
-      <c r="DU2" s="0" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>OneOctet</t>
         </is>
       </c>
-      <c r="DV2" s="0" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>B9600</t>
         </is>
       </c>
-      <c r="DW2" s="0" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>OneOctet</t>
         </is>
       </c>
-      <c r="DX2" s="0" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="DY2" s="0" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>IECSingleBit</t>
         </is>
       </c>
-      <c r="DZ2" s="0" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>IECSingleBit</t>
         </is>
       </c>
-      <c r="EA2" s="0" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="EB2" s="0" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>IECShortNormalized</t>
         </is>
       </c>
-      <c r="EC2" s="0" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="ED2" s="0" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="EE2" s="0" t="inlineStr">
+      <c r="EE2" t="inlineStr">
         <is>
           <t>Discrete</t>
         </is>
       </c>
-      <c r="EF2" s="0" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>IECShortNormalized</t>
         </is>
       </c>
-      <c r="EG2" s="0" t="inlineStr">
+      <c r="EG2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="EH2" s="0" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>IECSingleBit</t>
         </is>
       </c>
-      <c r="EI2" s="0" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>IECSingleBit</t>
         </is>
       </c>
-      <c r="EJ2" s="0" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="EK2" s="0" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>IECShortNormalized</t>
         </is>
       </c>
-      <c r="EL2" s="0" t="inlineStr">
+      <c r="EL2" t="inlineStr">
         <is>
           <t>RTU</t>
         </is>
       </c>
-      <c r="EM2" s="0" t="inlineStr">
+      <c r="EM2" t="inlineStr">
         <is>
           <t>OneOctet</t>
         </is>
       </c>
-      <c r="EN2" s="0" t="inlineStr">
+      <c r="EN2" t="inlineStr">
         <is>
           <t>RTU</t>
         </is>
       </c>
-      <c r="EO2" s="0" t="inlineStr">
+      <c r="EO2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="EP2" s="0" t="inlineStr">
+      <c r="EP2" t="inlineStr">
         <is>
           <t>IECSingleBit</t>
         </is>
       </c>
-      <c r="EQ2" s="0" t="inlineStr">
+      <c r="EQ2" t="inlineStr">
         <is>
           <t>IECSingleBit</t>
         </is>
       </c>
-      <c r="ER2" s="0" t="inlineStr">
+      <c r="ER2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="ES2" s="0" t="inlineStr">
+      <c r="ES2" t="inlineStr">
         <is>
           <t>IECShortNormalized</t>
         </is>
       </c>
-      <c r="ET2" s="0" t="inlineStr">
+      <c r="ET2" t="inlineStr">
         <is>
           <t>IECShortNormalized</t>
         </is>
       </c>
-      <c r="EU2" s="0" t="inlineStr">
+      <c r="EU2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="EV2" s="0" t="inlineStr">
+      <c r="EV2" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="EW2" s="0" t="inlineStr">
+      <c r="EW2" t="inlineStr">
         <is>
           <t>IECShortNormalized</t>
         </is>
       </c>
-      <c r="EX2" s="0" t="inlineStr">
+      <c r="EX2" t="inlineStr">
         <is>
           <t>IECShortNormalized</t>
         </is>
       </c>
-      <c r="EY2" s="0" t="inlineStr">
+      <c r="EY2" t="inlineStr">
         <is>
           <t>Discrete</t>
         </is>
       </c>
-      <c r="EZ2" s="0" t="inlineStr">
+      <c r="EZ2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="FA2" s="0" t="inlineStr">
+      <c r="FA2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="FB2" s="0" t="inlineStr">
+      <c r="FB2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="FC2" s="0" t="inlineStr">
+      <c r="FC2" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="FD2" s="0" t="inlineStr">
+      <c r="FD2" t="inlineStr">
         <is>
           <t>Discrete</t>
         </is>
       </c>
-      <c r="FE2" s="0" t="inlineStr">
+      <c r="FE2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="FF2" s="0" t="inlineStr">
+      <c r="FF2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="FG2" s="0" t="inlineStr">
+      <c r="FG2" t="inlineStr">
         <is>
           <t>Coil</t>
         </is>
       </c>
-      <c r="FH2" s="0" t="inlineStr">
+      <c r="FH2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="FI2" s="0" t="inlineStr">
+      <c r="FI2" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="FJ2" s="0" t="inlineStr">
+      <c r="FJ2" t="inlineStr">
         <is>
           <t>Coil</t>
         </is>
       </c>
-      <c r="FK2" s="0" t="inlineStr">
+      <c r="FK2" t="inlineStr">
         <is>
           <t>Discrete</t>
         </is>
       </c>
-      <c r="FL2" s="0" t="inlineStr">
+      <c r="FL2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="FM2" s="0" t="inlineStr">
+      <c r="FM2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="FN2" s="0" t="inlineStr">
+      <c r="FN2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="FO2" s="0" t="inlineStr">
+      <c r="FO2" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="FP2" s="0" t="inlineStr">
+      <c r="FP2" t="inlineStr">
         <is>
           <t>Discrete</t>
         </is>
       </c>
-      <c r="FQ2" s="0" t="inlineStr">
+      <c r="FQ2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="FR2" s="0" t="inlineStr">
+      <c r="FR2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="FS2" s="0" t="inlineStr">
+      <c r="FS2" t="inlineStr">
         <is>
           <t>Analog</t>
         </is>
       </c>
-      <c r="FT2" s="0" t="inlineStr">
+      <c r="FT2" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="FU2" s="0" t="inlineStr">
+      <c r="FU2" t="inlineStr">
         <is>
           <t>Discrete</t>
         </is>
       </c>
-      <c r="FV2" s="0" t="inlineStr">
+      <c r="FV2" t="inlineStr">
         <is>
           <t>Bool</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" s="82">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B3" s="0" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>DiscreteState</t>
         </is>
       </c>
-      <c r="D3" s="0" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Severidade 15</t>
         </is>
       </c>
-      <c r="E3" s="0" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Voltage</t>
         </is>
       </c>
-      <c r="F3" s="0" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>DoNotOperatorOpen</t>
         </is>
       </c>
-      <c r="G3" s="0" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>BAY</t>
         </is>
       </c>
-      <c r="H3" s="0" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>SwitchStatus</t>
         </is>
       </c>
-      <c r="I3" s="0" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Abnormal</t>
         </is>
       </c>
-      <c r="J3" s="0" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K3" s="0" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="L3" s="0" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
-      <c r="M3" s="0" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>MeasuredValue</t>
         </is>
       </c>
-      <c r="N3" s="0" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="O3" s="0" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Forward</t>
         </is>
       </c>
-      <c r="P3" s="0" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>SubstationControlSystem</t>
         </is>
       </c>
-      <c r="Q3" s="0" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>(UTC-11:00) Coordinated Universal Time-11</t>
         </is>
       </c>
-      <c r="R3" s="0" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>SwitchOnFirstRTUFailure</t>
         </is>
       </c>
-      <c r="S3" s="0" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Group8F</t>
         </is>
       </c>
-      <c r="T3" s="0" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Baker</t>
         </is>
       </c>
-      <c r="U3" s="0" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>SOEScan</t>
         </is>
       </c>
-      <c r="V3" s="0" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W3" s="0" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SelectWithValue</t>
         </is>
       </c>
-      <c r="X3" s="0" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SingleBitMCDA</t>
         </is>
       </c>
-      <c r="Y3" s="0" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>SectionB</t>
         </is>
       </c>
-      <c r="Z3" s="0" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>TwoCoord</t>
         </is>
       </c>
-      <c r="AA3" s="0" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>RaiseLower</t>
         </is>
       </c>
-      <c r="AB3" s="0" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="AC3" s="0" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>TwelveBitSignedTwoComplement</t>
         </is>
       </c>
-      <c r="AD3" s="0" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Int16</t>
         </is>
       </c>
-      <c r="AE3" s="0" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Class0123</t>
         </is>
       </c>
-      <c r="AF3" s="0" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>Serial</t>
         </is>
       </c>
-      <c r="AG3" s="0" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Diagnostic</t>
         </is>
       </c>
-      <c r="AH3" s="0" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>Sometimes</t>
         </is>
       </c>
-      <c r="AI3" s="0" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>BinaryInputEvent</t>
         </is>
       </c>
-      <c r="AJ3" s="0" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>DoubleBit</t>
         </is>
       </c>
-      <c r="AK3" s="0" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>MultiCoord</t>
         </is>
       </c>
-      <c r="AL3" s="0" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>PulseOn</t>
         </is>
       </c>
-      <c r="AM3" s="0" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>Int32</t>
         </is>
       </c>
-      <c r="AN3" s="0" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>WithAbsoluteTime</t>
         </is>
       </c>
-      <c r="AO3" s="0" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>BinaryInputWithFlags</t>
         </is>
       </c>
-      <c r="AP3" s="0" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>Class2</t>
         </is>
       </c>
-      <c r="AQ3" s="0" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>Int16WithFlag</t>
         </is>
       </c>
-      <c r="AR3" s="0" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>Int16WithFlag</t>
         </is>
       </c>
-      <c r="AS3" s="0" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>Version2000</t>
         </is>
       </c>
-      <c r="AT3" s="0" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>Block2</t>
         </is>
       </c>
-      <c r="AU3" s="0" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>Incoming</t>
         </is>
       </c>
-      <c r="AV3" s="0" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>Server</t>
         </is>
       </c>
-      <c r="AW3" s="0" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>Mace</t>
         </is>
       </c>
-      <c r="AX3" s="0" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>ManualInterval</t>
         </is>
       </c>
-      <c r="AY3" s="0" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Icc</t>
         </is>
       </c>
-      <c r="AZ3" s="0" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>Real</t>
         </is>
       </c>
-      <c r="BA3" s="0" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>CounterFreezeWithReset</t>
         </is>
       </c>
-      <c r="BB3" s="0" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>LoadDelay</t>
         </is>
       </c>
-      <c r="BC3" s="0" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>TwoOctets</t>
         </is>
       </c>
-      <c r="BD3" s="0" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>Balanced</t>
         </is>
       </c>
-      <c r="BE3" s="0" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="BF3" s="0" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>DialIn</t>
         </is>
       </c>
-      <c r="BG3" s="0" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>TelephoneNumber</t>
         </is>
       </c>
-      <c r="BH3" s="0" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>B200</t>
         </is>
       </c>
-      <c r="BI3" s="0" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>IECSingleBit</t>
         </is>
       </c>
-      <c r="BJ3" s="0" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>ShortPulse</t>
         </is>
       </c>
-      <c r="BK3" s="0" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>Off</t>
         </is>
       </c>
-      <c r="BL3" s="0" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>IECShortScaled</t>
         </is>
       </c>
-      <c r="BM3" s="0" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>IECRateShortTimestamp</t>
         </is>
       </c>
-      <c r="BN3" s="0" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>AnalogDeltaScan</t>
         </is>
       </c>
-      <c r="BO3" s="0" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>DigitalInputModule</t>
         </is>
       </c>
-      <c r="BP3" s="0" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>MultiBit</t>
         </is>
       </c>
-      <c r="BQ3" s="0" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>POMType</t>
         </is>
       </c>
-      <c r="BR3" s="0" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>TwoCoord</t>
         </is>
       </c>
-      <c r="BS3" s="0" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="BT3" s="0" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>FloatingPointModule</t>
         </is>
       </c>
-      <c r="BU3" s="0" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>TwelveBitSignedTwoComplement</t>
         </is>
       </c>
-      <c r="BV3" s="0" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>InputPointControl</t>
         </is>
       </c>
-      <c r="BW3" s="0" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>BigEndian</t>
         </is>
       </c>
-      <c r="BX3" s="0" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>ASCII</t>
         </is>
       </c>
-      <c r="BY3" s="0" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>DiscreteInput</t>
         </is>
       </c>
-      <c r="BZ3" s="0" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>TwoCoords</t>
         </is>
       </c>
-      <c r="CA3" s="0" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>UShort</t>
         </is>
       </c>
-      <c r="CB3" s="0" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>CRC16bit</t>
         </is>
       </c>
-      <c r="CC3" s="0" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>StatusScan</t>
         </is>
       </c>
-      <c r="CD3" s="0" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>DoubleCoord</t>
         </is>
       </c>
-      <c r="CE3" s="0" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>AllStatusScan</t>
         </is>
       </c>
-      <c r="CF3" s="0" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>MemoryStatus</t>
         </is>
       </c>
-      <c r="CG3" s="0" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>DoubleCoord</t>
         </is>
       </c>
-      <c r="CH3" s="0" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>Unsigned</t>
         </is>
       </c>
-      <c r="CI3" s="0" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>Int</t>
         </is>
       </c>
-      <c r="CJ3" s="0" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="CK3" s="0" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>TerminalServer</t>
         </is>
       </c>
-      <c r="CL3" s="0" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>AutoSelectWithValue</t>
         </is>
       </c>
-      <c r="CN3" s="0" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="CO3" s="0" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="CS3" s="0" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>AutoSelectWithValue</t>
         </is>
       </c>
-      <c r="CT3" s="0" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>DoubleBit</t>
         </is>
       </c>
-      <c r="CU3" s="0" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="CV3" s="0" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>AutoSelectWithValue</t>
         </is>
       </c>
-      <c r="CW3" s="0" t="inlineStr">
+      <c r="CW3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="CY3" s="0" t="inlineStr">
+      <c r="CY3" t="inlineStr">
         <is>
           <t>AutoSelectWithValue</t>
         </is>
       </c>
-      <c r="DB3" s="0" t="inlineStr">
+      <c r="DB3" t="inlineStr">
         <is>
           <t>AutoSelectWithValue</t>
         </is>
       </c>
-      <c r="DC3" s="0" t="inlineStr">
+      <c r="DC3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="DD3" s="0" t="inlineStr">
+      <c r="DD3" t="inlineStr">
         <is>
           <t>AutoSelectWithValue</t>
         </is>
       </c>
-      <c r="DE3" s="0" t="inlineStr">
+      <c r="DE3" t="inlineStr">
         <is>
           <t>DSTS</t>
         </is>
       </c>
-      <c r="DF3" s="0" t="inlineStr">
+      <c r="DF3" t="inlineStr">
         <is>
           <t>DSTS</t>
         </is>
       </c>
-      <c r="DH3" s="0" t="inlineStr">
+      <c r="DH3" t="inlineStr">
         <is>
           <t>Discrete</t>
         </is>
       </c>
-      <c r="DI3" s="0" t="inlineStr">
+      <c r="DI3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="DJ3" s="0" t="inlineStr">
+      <c r="DJ3" t="inlineStr">
         <is>
           <t>RealQuality</t>
         </is>
       </c>
-      <c r="DK3" s="0" t="inlineStr">
+      <c r="DK3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="DM3" s="0" t="inlineStr">
+      <c r="DM3" t="inlineStr">
         <is>
           <t>RealQuality</t>
         </is>
       </c>
-      <c r="DO3" s="0" t="inlineStr">
+      <c r="DO3" t="inlineStr">
         <is>
           <t>Discrete</t>
         </is>
       </c>
-      <c r="DP3" s="0" t="inlineStr">
+      <c r="DP3" t="inlineStr">
         <is>
           <t>RealQuality</t>
         </is>
       </c>
-      <c r="DQ3" s="0" t="inlineStr">
+      <c r="DQ3" t="inlineStr">
         <is>
           <t>ModemBank</t>
         </is>
       </c>
-      <c r="DR3" s="0" t="inlineStr">
+      <c r="DR3" t="inlineStr">
         <is>
           <t>TwoOctets</t>
         </is>
       </c>
-      <c r="DS3" s="0" t="inlineStr">
+      <c r="DS3" t="inlineStr">
         <is>
           <t>TwoOctets</t>
         </is>
       </c>
-      <c r="DT3" s="0" t="inlineStr">
+      <c r="DT3" t="inlineStr">
         <is>
           <t>TwoOctets</t>
         </is>
       </c>
-      <c r="DU3" s="0" t="inlineStr">
+      <c r="DU3" t="inlineStr">
         <is>
           <t>TwoOctets</t>
         </is>
       </c>
-      <c r="DW3" s="0" t="inlineStr">
+      <c r="DW3" t="inlineStr">
         <is>
           <t>TwoOctets</t>
         </is>
       </c>
-      <c r="DY3" s="0" t="inlineStr">
+      <c r="DY3" t="inlineStr">
         <is>
           <t>IECDoubleBit</t>
         </is>
       </c>
-      <c r="DZ3" s="0" t="inlineStr">
+      <c r="DZ3" t="inlineStr">
         <is>
           <t>IECDoubleBit</t>
         </is>
       </c>
-      <c r="EA3" s="0" t="inlineStr">
+      <c r="EA3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="EB3" s="0" t="inlineStr">
+      <c r="EB3" t="inlineStr">
         <is>
           <t>IECShortScaled</t>
         </is>
       </c>
-      <c r="EC3" s="0" t="inlineStr">
+      <c r="EC3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="EF3" s="0" t="inlineStr">
+      <c r="EF3" t="inlineStr">
         <is>
           <t>IECShortScaled</t>
         </is>
       </c>
-      <c r="EH3" s="0" t="inlineStr">
+      <c r="EH3" t="inlineStr">
         <is>
           <t>IECDoubleBit</t>
         </is>
       </c>
-      <c r="EI3" s="0" t="inlineStr">
+      <c r="EI3" t="inlineStr">
         <is>
           <t>IECDoubleBit</t>
         </is>
       </c>
-      <c r="EJ3" s="0" t="inlineStr">
+      <c r="EJ3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="EK3" s="0" t="inlineStr">
+      <c r="EK3" t="inlineStr">
         <is>
           <t>IECShortScaled</t>
         </is>
       </c>
-      <c r="EM3" s="0" t="inlineStr">
+      <c r="EM3" t="inlineStr">
         <is>
           <t>TwoOctets</t>
         </is>
       </c>
-      <c r="EP3" s="0" t="inlineStr">
+      <c r="EP3" t="inlineStr">
         <is>
           <t>IECDoubleBit</t>
         </is>
       </c>
-      <c r="EQ3" s="0" t="inlineStr">
+      <c r="EQ3" t="inlineStr">
         <is>
           <t>IECDoubleBit</t>
         </is>
       </c>
-      <c r="ER3" s="0" t="inlineStr">
+      <c r="ER3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="ES3" s="0" t="inlineStr">
+      <c r="ES3" t="inlineStr">
         <is>
           <t>IECShortScaled</t>
         </is>
       </c>
-      <c r="ET3" s="0" t="inlineStr">
+      <c r="ET3" t="inlineStr">
         <is>
           <t>IECShortScaled</t>
         </is>
       </c>
-      <c r="EU3" s="0" t="inlineStr">
+      <c r="EU3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="EW3" s="0" t="inlineStr">
+      <c r="EW3" t="inlineStr">
         <is>
           <t>IECShortScaled</t>
         </is>
       </c>
-      <c r="EX3" s="0" t="inlineStr">
+      <c r="EX3" t="inlineStr">
         <is>
           <t>IECShortScaled</t>
         </is>
       </c>
-      <c r="FA3" s="0" t="inlineStr">
+      <c r="FA3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="FB3" s="0" t="inlineStr">
+      <c r="FB3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="FF3" s="0" t="inlineStr">
+      <c r="FF3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="FG3" s="0" t="inlineStr">
+      <c r="FG3" t="inlineStr">
         <is>
           <t>HoldingRegister</t>
         </is>
       </c>
-      <c r="FH3" s="0" t="inlineStr">
+      <c r="FH3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="FJ3" s="0" t="inlineStr">
+      <c r="FJ3" t="inlineStr">
         <is>
           <t>HoldingRegister</t>
         </is>
       </c>
-      <c r="FM3" s="0" t="inlineStr">
+      <c r="FM3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="FN3" s="0" t="inlineStr">
+      <c r="FN3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="FR3" s="0" t="inlineStr">
+      <c r="FR3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="FS3" s="0" t="inlineStr">
+      <c r="FS3" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="FV3" s="0" t="inlineStr">
+      <c r="FV3" t="inlineStr">
         <is>
           <t>Int</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" s="82">
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>AnalogHigh</t>
         </is>
       </c>
-      <c r="D4" s="0" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Severidade 14</t>
         </is>
       </c>
-      <c r="E4" s="0" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="F4" s="0" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>DoNotAutoClose</t>
         </is>
       </c>
-      <c r="G4" s="0" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>BASEVOLTAGE</t>
         </is>
       </c>
-      <c r="H4" s="0" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="I4" s="0" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
-      <c r="J4" s="0" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="K4" s="0" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Secondary</t>
         </is>
       </c>
-      <c r="L4" s="0" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>ReadWrite</t>
         </is>
       </c>
-      <c r="M4" s="0" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>ControlSetValue</t>
         </is>
       </c>
-      <c r="N4" s="0" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="O4" s="0" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P4" s="0" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>ControlCenter</t>
         </is>
       </c>
-      <c r="Q4" s="0" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>(UTC-10:00) Aleutian Islands</t>
         </is>
       </c>
-      <c r="R4" s="0" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>SwitchOnAllRTUFailure</t>
         </is>
       </c>
-      <c r="V4" s="0" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Counter</t>
         </is>
       </c>
-      <c r="W4" s="0" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SelectWithoutValue</t>
         </is>
       </c>
-      <c r="X4" s="0" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>MultiBit</t>
         </is>
       </c>
-      <c r="Z4" s="0" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>MultiCoord</t>
         </is>
       </c>
-      <c r="AB4" s="0" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Raise</t>
         </is>
       </c>
-      <c r="AC4" s="0" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>SixBitUnsigned</t>
         </is>
       </c>
-      <c r="AD4" s="0" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Float</t>
         </is>
       </c>
-      <c r="AE4" s="0" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>ScanTable</t>
         </is>
       </c>
-      <c r="AG4" s="0" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="AH4" s="0" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="AI4" s="0" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>DoubleBinaryInput</t>
         </is>
       </c>
-      <c r="AJ4" s="0" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>MultiCoord</t>
         </is>
       </c>
-      <c r="AL4" s="0" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>PulseOff</t>
         </is>
       </c>
-      <c r="AM4" s="0" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>Int16</t>
         </is>
       </c>
-      <c r="AN4" s="0" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>WithRelativeTime</t>
         </is>
       </c>
-      <c r="AO4" s="0" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>DoubleBitBinaryInputPackedFormat</t>
         </is>
       </c>
-      <c r="AP4" s="0" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>Class3</t>
         </is>
       </c>
-      <c r="AQ4" s="0" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>Int32WithoutFlag</t>
         </is>
       </c>
-      <c r="AR4" s="0" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>Int32WithoutFlag</t>
         </is>
       </c>
-      <c r="AT4" s="0" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>Block3</t>
         </is>
       </c>
-      <c r="AV4" s="0" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>Peer</t>
         </is>
       </c>
-      <c r="AW4" s="0" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>SSL</t>
         </is>
       </c>
-      <c r="AX4" s="0" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>AutoAll</t>
         </is>
       </c>
-      <c r="AZ4" s="0" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="BA4" s="0" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>CounterFreezeWithoutReset</t>
         </is>
       </c>
-      <c r="BB4" s="0" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>DelayAcq</t>
         </is>
       </c>
-      <c r="BC4" s="0" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>ThreeOctets</t>
         </is>
       </c>
-      <c r="BE4" s="0" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>Never</t>
         </is>
       </c>
-      <c r="BG4" s="0" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="BH4" s="0" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>B300</t>
         </is>
       </c>
-      <c r="BI4" s="0" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>IECDoubleBit</t>
         </is>
       </c>
-      <c r="BJ4" s="0" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>LongPulse</t>
         </is>
       </c>
-      <c r="BL4" s="0" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>IECFloat</t>
         </is>
       </c>
-      <c r="BM4" s="0" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>IECRate</t>
         </is>
       </c>
-      <c r="BN4" s="0" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>DigitalCOSTimeTagged</t>
         </is>
       </c>
-      <c r="BP4" s="0" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>MultiBitBCD</t>
         </is>
       </c>
-      <c r="BQ4" s="0" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>DOMType</t>
         </is>
       </c>
-      <c r="BR4" s="0" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>MultiCoord</t>
         </is>
       </c>
-      <c r="BS4" s="0" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>Raise</t>
         </is>
       </c>
-      <c r="BT4" s="0" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>AnalogInputModuleDCM</t>
         </is>
       </c>
-      <c r="BU4" s="0" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>TwelveBitUnsigned</t>
         </is>
       </c>
-      <c r="BV4" s="0" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>FloatingPointOP</t>
         </is>
       </c>
-      <c r="BX4" s="0" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>RTU</t>
         </is>
       </c>
-      <c r="BY4" s="0" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>InputRegister</t>
         </is>
       </c>
-      <c r="BZ4" s="0" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>MultiCoord</t>
         </is>
       </c>
-      <c r="CA4" s="0" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>Int32</t>
         </is>
       </c>
-      <c r="CC4" s="0" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>AnalogScan</t>
         </is>
       </c>
-      <c r="CD4" s="0" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>MultiCoord</t>
         </is>
       </c>
-      <c r="CE4" s="0" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>MomentaryStatusScan</t>
         </is>
       </c>
-      <c r="CF4" s="0" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>LatchingStatus</t>
         </is>
       </c>
-      <c r="CG4" s="0" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>MultiCoord</t>
         </is>
       </c>
-      <c r="CI4" s="0" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="CJ4" s="0" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>Flags</t>
         </is>
       </c>
-      <c r="CS4" s="0" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>DirectNoAck</t>
         </is>
       </c>
-      <c r="CT4" s="0" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>MultiCoord</t>
         </is>
       </c>
-      <c r="CV4" s="0" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>DirectNoAck</t>
         </is>
       </c>
-      <c r="CY4" s="0" t="inlineStr">
+      <c r="CY4" t="inlineStr">
         <is>
           <t>DirectNoAck</t>
         </is>
       </c>
-      <c r="DB4" s="0" t="inlineStr">
+      <c r="DB4" t="inlineStr">
         <is>
           <t>DirectNoAck</t>
         </is>
       </c>
-      <c r="DD4" s="0" t="inlineStr">
+      <c r="DD4" t="inlineStr">
         <is>
           <t>DirectNoAck</t>
         </is>
       </c>
-      <c r="DH4" s="0" t="inlineStr">
+      <c r="DH4" t="inlineStr">
         <is>
           <t>StateSupp</t>
         </is>
       </c>
-      <c r="DJ4" s="0" t="inlineStr">
+      <c r="DJ4" t="inlineStr">
         <is>
           <t>RealQualityTimeTag</t>
         </is>
       </c>
-      <c r="DM4" s="0" t="inlineStr">
+      <c r="DM4" t="inlineStr">
         <is>
           <t>RealQualityTimeTag</t>
         </is>
       </c>
-      <c r="DO4" s="0" t="inlineStr">
+      <c r="DO4" t="inlineStr">
         <is>
           <t>StateSupp</t>
         </is>
       </c>
-      <c r="DP4" s="0" t="inlineStr">
+      <c r="DP4" t="inlineStr">
         <is>
           <t>RealQualityTimeTag</t>
         </is>
       </c>
-      <c r="DQ4" s="0" t="inlineStr">
+      <c r="DQ4" t="inlineStr">
         <is>
           <t>TerminalServer</t>
         </is>
       </c>
-      <c r="DU4" s="0" t="inlineStr">
+      <c r="DU4" t="inlineStr">
         <is>
           <t>Undefined</t>
         </is>
       </c>
-      <c r="DW4" s="0" t="inlineStr">
+      <c r="DW4" t="inlineStr">
         <is>
           <t>Undefined</t>
         </is>
       </c>
-      <c r="DY4" s="0" t="inlineStr">
+      <c r="DY4" t="inlineStr">
         <is>
           <t>IECStepPosition</t>
         </is>
       </c>
-      <c r="DZ4" s="0" t="inlineStr">
+      <c r="DZ4" t="inlineStr">
         <is>
           <t>IECStepPosition</t>
         </is>
       </c>
-      <c r="EB4" s="0" t="inlineStr">
+      <c r="EB4" t="inlineStr">
         <is>
           <t>IECFloat</t>
         </is>
       </c>
-      <c r="EF4" s="0" t="inlineStr">
+      <c r="EF4" t="inlineStr">
         <is>
           <t>IECFloat</t>
         </is>
       </c>
-      <c r="EH4" s="0" t="inlineStr">
+      <c r="EH4" t="inlineStr">
         <is>
           <t>IECStepPosition</t>
         </is>
       </c>
-      <c r="EI4" s="0" t="inlineStr">
+      <c r="EI4" t="inlineStr">
         <is>
           <t>IECStepPosition</t>
         </is>
       </c>
-      <c r="EK4" s="0" t="inlineStr">
+      <c r="EK4" t="inlineStr">
         <is>
           <t>IECFloat</t>
         </is>
       </c>
-      <c r="EP4" s="0" t="inlineStr">
+      <c r="EP4" t="inlineStr">
         <is>
           <t>IECStepPosition</t>
         </is>
       </c>
-      <c r="EQ4" s="0" t="inlineStr">
+      <c r="EQ4" t="inlineStr">
         <is>
           <t>IECStepPosition</t>
         </is>
       </c>
-      <c r="ES4" s="0" t="inlineStr">
+      <c r="ES4" t="inlineStr">
         <is>
           <t>IECFloat</t>
         </is>
       </c>
-      <c r="ET4" s="0" t="inlineStr">
+      <c r="ET4" t="inlineStr">
         <is>
           <t>IECFloat</t>
         </is>
       </c>
-      <c r="EW4" s="0" t="inlineStr">
+      <c r="EW4" t="inlineStr">
         <is>
           <t>IECFloat</t>
         </is>
       </c>
-      <c r="EX4" s="0" t="inlineStr">
+      <c r="EX4" t="inlineStr">
         <is>
           <t>IECFloat</t>
         </is>
       </c>
-      <c r="FV4" s="0" t="inlineStr">
+      <c r="FV4" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" s="82">
-      <c r="C5" s="0" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>AnalogLow</t>
         </is>
       </c>
-      <c r="D5" s="0" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Severidade 13</t>
         </is>
       </c>
-      <c r="E5" s="0" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>ActivePower</t>
         </is>
       </c>
-      <c r="F5" s="0" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>DoNotAutoOpen</t>
         </is>
       </c>
-      <c r="G5" s="0" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>NETWORKINFO</t>
         </is>
       </c>
-      <c r="H5" s="0" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>OperationCount</t>
         </is>
       </c>
-      <c r="J5" s="0" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="K5" s="0" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Tertiary</t>
         </is>
       </c>
-      <c r="M5" s="0" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>ControlBandwidth</t>
         </is>
       </c>
-      <c r="N5" s="0" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>mV</t>
         </is>
       </c>
-      <c r="P5" s="0" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>IED</t>
         </is>
       </c>
-      <c r="Q5" s="0" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>(UTC-10:00) Hawaii</t>
         </is>
       </c>
-      <c r="R5" s="0" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>CostFactorWithAvailabilityCheck</t>
         </is>
       </c>
-      <c r="V5" s="0" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>SmartMeter</t>
         </is>
       </c>
-      <c r="W5" s="0" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>AutoSelectWithValue</t>
         </is>
       </c>
-      <c r="X5" s="0" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>MultiBitBCD</t>
         </is>
       </c>
-      <c r="AB5" s="0" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Lower</t>
         </is>
       </c>
-      <c r="AC5" s="0" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>TwelveBitUnsigned</t>
         </is>
       </c>
-      <c r="AG5" s="0" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="AI5" s="0" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>DoubleBinaryInputEvent</t>
         </is>
       </c>
-      <c r="AJ5" s="0" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>MultiCoordBCD</t>
         </is>
       </c>
-      <c r="AL5" s="0" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>LatchOn</t>
         </is>
       </c>
-      <c r="AM5" s="0" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>Float</t>
         </is>
       </c>
-      <c r="AO5" s="0" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>DoubleBitBinaryInputWithFlags</t>
         </is>
       </c>
-      <c r="AP5" s="0" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AQ5" s="0" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>Int16WithoutFlag</t>
         </is>
       </c>
-      <c r="AR5" s="0" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>Int16WithoutFlag</t>
         </is>
       </c>
-      <c r="AT5" s="0" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>Block4</t>
         </is>
       </c>
-      <c r="AX5" s="0" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>AutoReal</t>
         </is>
       </c>
-      <c r="AZ5" s="0" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>Discrete</t>
         </is>
       </c>
-      <c r="BA5" s="0" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>CounterReset</t>
         </is>
       </c>
-      <c r="BC5" s="0" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>Undefined</t>
         </is>
       </c>
-      <c r="BG5" s="0" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>Delay</t>
         </is>
       </c>
-      <c r="BH5" s="0" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>B600</t>
         </is>
       </c>
-      <c r="BI5" s="0" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>IECStepPosition</t>
         </is>
       </c>
-      <c r="BJ5" s="0" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>Persistent</t>
         </is>
       </c>
-      <c r="BL5" s="0" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>IECShortNormalizedTimestamp</t>
         </is>
       </c>
-      <c r="BN5" s="0" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>DigitalUnconditional</t>
         </is>
       </c>
-      <c r="BQ5" s="0" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>InputPointControl</t>
         </is>
       </c>
-      <c r="BS5" s="0" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>Lower</t>
         </is>
       </c>
-      <c r="BU5" s="0" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>FloatingPoint</t>
         </is>
       </c>
-      <c r="BY5" s="0" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>HoldingRegister</t>
         </is>
       </c>
-      <c r="CA5" s="0" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>UInt32</t>
         </is>
       </c>
-      <c r="CC5" s="0" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>SetpointScan</t>
         </is>
       </c>
-      <c r="CE5" s="0" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>MemoryStatusScan</t>
         </is>
       </c>
-      <c r="CF5" s="0" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>Multibit</t>
         </is>
       </c>
-      <c r="CG5" s="0" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>RaiseLower</t>
         </is>
       </c>
-      <c r="CI5" s="0" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="CJ5" s="0" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="DH5" s="0" t="inlineStr">
+      <c r="DH5" t="inlineStr">
         <is>
           <t>StateQuality</t>
         </is>
       </c>
-      <c r="DJ5" s="0" t="inlineStr">
+      <c r="DJ5" t="inlineStr">
         <is>
           <t>RealExtended</t>
         </is>
       </c>
-      <c r="DM5" s="0" t="inlineStr">
+      <c r="DM5" t="inlineStr">
         <is>
           <t>RealExtended</t>
         </is>
       </c>
-      <c r="DO5" s="0" t="inlineStr">
+      <c r="DO5" t="inlineStr">
         <is>
           <t>StateQuality</t>
         </is>
       </c>
-      <c r="DP5" s="0" t="inlineStr">
+      <c r="DP5" t="inlineStr">
         <is>
           <t>RealExtended</t>
         </is>
       </c>
-      <c r="DY5" s="0" t="inlineStr">
+      <c r="DY5" t="inlineStr">
         <is>
           <t>IECBitstring</t>
         </is>
       </c>
-      <c r="DZ5" s="0" t="inlineStr">
+      <c r="DZ5" t="inlineStr">
         <is>
           <t>IECBitstring</t>
         </is>
       </c>
-      <c r="EH5" s="0" t="inlineStr">
+      <c r="EH5" t="inlineStr">
         <is>
           <t>IECBitstring</t>
         </is>
       </c>
-      <c r="EI5" s="0" t="inlineStr">
+      <c r="EI5" t="inlineStr">
         <is>
           <t>IECBitstring</t>
         </is>
       </c>
-      <c r="EP5" s="0" t="inlineStr">
+      <c r="EP5" t="inlineStr">
         <is>
           <t>IECBitstring</t>
         </is>
       </c>
-      <c r="EQ5" s="0" t="inlineStr">
+      <c r="EQ5" t="inlineStr">
         <is>
           <t>IECBitstring</t>
         </is>
       </c>
-      <c r="ES5" s="0" t="inlineStr">
+      <c r="ES5" t="inlineStr">
         <is>
           <t>IECShortNormalizedTimestamp</t>
         </is>
       </c>
-      <c r="ET5" s="0" t="inlineStr">
+      <c r="ET5" t="inlineStr">
         <is>
           <t>IECShortNormalizedTimestamp</t>
         </is>
       </c>
-      <c r="EW5" s="0" t="inlineStr">
+      <c r="EW5" t="inlineStr">
         <is>
           <t>IECShortNormalizedTimestamp</t>
         </is>
       </c>
-      <c r="EX5" s="0" t="inlineStr">
+      <c r="EX5" t="inlineStr">
         <is>
           <t>IECShortNormalizedTimestamp</t>
         </is>
       </c>
-      <c r="FV5" s="0" t="inlineStr">
+      <c r="FV5" t="inlineStr">
         <is>
           <t>String</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AnalogCreep</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Severidade 12</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ReactivePower</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>WarnOnOpen</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FAULTINDICATORC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TapPosition</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ControlDelay</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SmartMeter</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>(UTC-09:30) Marquesas Islands</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>AutoSelectWithoutValue</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>SingleBitMCDB</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>RemoteStatusByte</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>BinaryOutput</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>LatchOff</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>FloatWithFlag</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>Block5</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>AutoDiscrete</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>StateSupp</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>B1200</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>IECBitstring</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>IECShortScaledTimestamp</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>FloatingPointUnconditional</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>PointOff</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>FifteenBitSignedMagnitude</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>Float</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>LatchingStatusScan</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>ASignal</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>AlarmLimit</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>DiscreteQuality</t>
+        </is>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>RealQualityTimeTagExtended</t>
+        </is>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>RealQualityTimeTagExtended</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>DiscreteQuality</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>RealQualityTimeTagExtended</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>IECMultiBit</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr">
+        <is>
+          <t>IECMultiBit</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>IECMultiBit</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>IECMultiBit</t>
+        </is>
+      </c>
+      <c r="EP6" t="inlineStr">
+        <is>
+          <t>IECMultiBit</t>
+        </is>
+      </c>
+      <c r="EQ6" t="inlineStr">
+        <is>
+          <t>IECMultiBit</t>
+        </is>
+      </c>
+      <c r="ES6" t="inlineStr">
+        <is>
+          <t>IECShortScaledTimestamp</t>
+        </is>
+      </c>
+      <c r="ET6" t="inlineStr">
+        <is>
+          <t>IECShortScaledTimestamp</t>
+        </is>
+      </c>
+      <c r="EW6" t="inlineStr">
+        <is>
+          <t>IECShortScaledTimestamp</t>
+        </is>
+      </c>
+      <c r="EX6" t="inlineStr">
+        <is>
+          <t>IECShortScaledTimestamp</t>
+        </is>
+      </c>
+      <c r="FV6" t="inlineStr">
+        <is>
+          <t>ASignal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AnalogGrowth</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Severidade 11</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CosPhi</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>WarnOnClose</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>POWERTRC2W</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TapIncrement</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>BN</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ControlSubDelay</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>kA</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ModemBank</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>(UTC-09:00) Alaska</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>DirectNoAck</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>SingleBitMCDC</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>BinaryOutputEvent</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>ClosePulseOn</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>DoubleWithFlag</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>AutoState</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>RealQuality</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>B2400</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>IECMultiBit</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>IECFloatTimestamp</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>FloatingPointDelta</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>PointOn</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>FifteenBitSignedTwoComplement</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>StatusExceptionScan</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>DSignal</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>StateSuppQuality</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>StateSuppQuality</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>IECSingleBitTimestamp</t>
+        </is>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
+          <t>IECSingleBitTimestamp</t>
+        </is>
+      </c>
+      <c r="EP7" t="inlineStr">
+        <is>
+          <t>IECSingleBitTimestamp</t>
+        </is>
+      </c>
+      <c r="EQ7" t="inlineStr">
+        <is>
+          <t>IECSingleBitTimestamp</t>
+        </is>
+      </c>
+      <c r="ES7" t="inlineStr">
+        <is>
+          <t>IECFloatTimestamp</t>
+        </is>
+      </c>
+      <c r="ET7" t="inlineStr">
+        <is>
+          <t>IECFloatTimestamp</t>
+        </is>
+      </c>
+      <c r="EW7" t="inlineStr">
+        <is>
+          <t>IECFloatTimestamp</t>
+        </is>
+      </c>
+      <c r="EX7" t="inlineStr">
+        <is>
+          <t>IECFloatTimestamp</t>
+        </is>
+      </c>
+      <c r="FV7" t="inlineStr">
+        <is>
+          <t>DSignal</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AnalogFlatline</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Severidade 10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>POWERTRC3W</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ControlLimitHigh</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>mA</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>DSTS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>(UTC-09:00) Coordinated Universal Time-09</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>DoubleBitMCDA</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>BinaryCounter</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>TripPulseOn</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>StateQuality</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>B4800</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>IECSingleBitTimestamp</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>IECShortNormalizedNoQuality</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>FloatingPointCOSTimeTagged</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>SinglePoleOperate</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>FifteenBitUnsigned</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>ReadInternalStatus</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>BoolArray</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>StateQualityTimeTag</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>StateQualityTimeTag</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>IECDoubleBitTimestamp</t>
+        </is>
+      </c>
+      <c r="EH8" t="inlineStr">
+        <is>
+          <t>IECDoubleBitTimestamp</t>
+        </is>
+      </c>
+      <c r="EP8" t="inlineStr">
+        <is>
+          <t>IECDoubleBitTimestamp</t>
+        </is>
+      </c>
+      <c r="EQ8" t="inlineStr">
+        <is>
+          <t>IECDoubleBitTimestamp</t>
+        </is>
+      </c>
+      <c r="ES8" t="inlineStr">
+        <is>
+          <t>IECShortNormalizedNoQuality</t>
+        </is>
+      </c>
+      <c r="ET8" t="inlineStr">
+        <is>
+          <t>IECShortNormalizedNoQuality</t>
+        </is>
+      </c>
+      <c r="EW8" t="inlineStr">
+        <is>
+          <t>IECShortNormalizedNoQuality</t>
+        </is>
+      </c>
+      <c r="EX8" t="inlineStr">
+        <is>
+          <t>IECShortNormalizedNoQuality</t>
+        </is>
+      </c>
+      <c r="FV8" t="inlineStr">
+        <is>
+          <t>ASignalArray</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AnalogDrop</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Severidade 9</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SYNCMACHINEC</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>LoadBonus</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>BCN</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ControlLimitLow</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>TerminalServer</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>(UTC-08:00) Baja California</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>DoubleBitMCDB</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>FrozenCounter</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>ClosePulseOff</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>DiscreteQuality</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>B9600</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>IECDoubleBitTimestamp</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>IECShortNormalizedShortTimestamp</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>CustomPayload0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>ClearInternalStatus</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>IntArray</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>DiscreteQualityTimeTag</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>DiscreteQualityTimeTag</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>IECStepPositionTimestamp</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>IECStepPositionTimestamp</t>
+        </is>
+      </c>
+      <c r="EP9" t="inlineStr">
+        <is>
+          <t>IECStepPositionTimestamp</t>
+        </is>
+      </c>
+      <c r="EQ9" t="inlineStr">
+        <is>
+          <t>IECStepPositionTimestamp</t>
+        </is>
+      </c>
+      <c r="FV9" t="inlineStr">
+        <is>
+          <t>DSignalArray</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AnalogRTN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Severidade 8</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ActiveEnergy</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OutOfOrder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CAPACITORC</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ReclosingEnabled</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ControlSlopeReal</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>(UTC-08:00) Coordinated Universal Time-08</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>DoubleBitMCDC</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>CounterEvent</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>TripPulseOff</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>StateSuppQuality</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>B19200</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>IECStepPositionTimestamp</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>IECShortScaledShortTimestamp</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>CustomPayload1</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>StatusAcknowledge</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>DoubleArray</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>StateSuppQualityTimeTag</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>StateSuppQualityTimeTag</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>IECBitstringTimestamp</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>IECBitstringTimestamp</t>
+        </is>
+      </c>
+      <c r="EP10" t="inlineStr">
+        <is>
+          <t>IECBitstringTimestamp</t>
+        </is>
+      </c>
+      <c r="EQ10" t="inlineStr">
+        <is>
+          <t>IECBitstringTimestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TransformerOverload</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Severidade 7</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ReactiveEnergy</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Malfunctioning</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PETERSENCOILC</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ControlActiveSetting</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AN</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ControlSlopeImag</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>(UTC-08:00) Pacific Time (US &amp; Canada)</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>FrozenCounterEvent</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>CloseLatchOn</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>RealQualityTimeTag</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>B38400</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>IECBitstringTimestamp</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>IECFloatShortTimestamp</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>CustomPayload32</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>StringArray</t>
+        </is>
+      </c>
+      <c r="DH11" t="inlineStr">
+        <is>
+          <t>StateExtended</t>
+        </is>
+      </c>
+      <c r="DO11" t="inlineStr">
+        <is>
+          <t>StateExtended</t>
+        </is>
+      </c>
+      <c r="DZ11" t="inlineStr">
+        <is>
+          <t>IECMultiBitTimestamp</t>
+        </is>
+      </c>
+      <c r="EH11" t="inlineStr">
+        <is>
+          <t>IECMultiBitTimestamp</t>
+        </is>
+      </c>
+      <c r="EP11" t="inlineStr">
+        <is>
+          <t>IECMultiBitTimestamp</t>
+        </is>
+      </c>
+      <c r="EQ11" t="inlineStr">
+        <is>
+          <t>IECMultiBitTimestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LineOverload</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Severidade 6</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ApparentPower</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AlarmInhibit</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>JUMPERC</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Refresh</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>FaultRecorder</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>kVAr</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>(UTC-07:00) Arizona</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>AnalogInput</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>TripLatchOn</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>StateQualityTimeTag</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>B56000</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>IECMultiBitTimestamp</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>ASignalArray</t>
+        </is>
+      </c>
+      <c r="DH12" t="inlineStr">
+        <is>
+          <t>DiscreteExtended</t>
+        </is>
+      </c>
+      <c r="DO12" t="inlineStr">
+        <is>
+          <t>DiscreteExtended</t>
+        </is>
+      </c>
+      <c r="DZ12" t="inlineStr">
+        <is>
+          <t>IECSingleBitShortTimestamp</t>
+        </is>
+      </c>
+      <c r="EH12" t="inlineStr">
+        <is>
+          <t>IECSingleBitShortTimestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AnalogReasonability</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Severidade 5</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>VoltageAngle</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AlarmAudioInhibit</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DISCONNECTORC</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>VoltageIndex1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>WeatherData</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>MVAr</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>(UTC-07:00) La Paz, Mazatlan</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>FrozenAnalogInput</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>CloseLatchOff</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>DiscreteQualityTimeTag</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>B64000</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>IECSingleBitShortTimestamp</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>DSignalArray</t>
+        </is>
+      </c>
+      <c r="DH13" t="inlineStr">
+        <is>
+          <t>StateSuppExtended</t>
+        </is>
+      </c>
+      <c r="DO13" t="inlineStr">
+        <is>
+          <t>StateSuppExtended</t>
+        </is>
+      </c>
+      <c r="DZ13" t="inlineStr">
+        <is>
+          <t>IECDoubleBitShortTimestamp</t>
+        </is>
+      </c>
+      <c r="EH13" t="inlineStr">
+        <is>
+          <t>IECDoubleBitShortTimestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SystemAlarm</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Severidade 4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>StopProcessing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SECTIONALIZERC</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>VoltageIndex2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>BellwetherMeter</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>VAr</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>(UTC-07:00) Mountain Time (US &amp; Canada)</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>AnalogInputEvent</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>TripLatchOff</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>StateSuppQualityTimeTag</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>IECDoubleBitShortTimestamp</t>
+        </is>
+      </c>
+      <c r="DH14" t="inlineStr">
+        <is>
+          <t>StateQualityTimeTagExtended</t>
+        </is>
+      </c>
+      <c r="DO14" t="inlineStr">
+        <is>
+          <t>StateQualityTimeTagExtended</t>
+        </is>
+      </c>
+      <c r="DZ14" t="inlineStr">
+        <is>
+          <t>IECStepPositionShortTimestamp</t>
+        </is>
+      </c>
+      <c r="EH14" t="inlineStr">
+        <is>
+          <t>IECStepPositionShortTimestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DOMAlarm</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Severidade 3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Discrete</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PointTest</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LOADBREAKERC</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>LoadFlowEnabled</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ABN</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>RecloseDelay</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>(UTC-07:00) Yukon</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>FrozenAnalogInputEvent</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>RealExtended</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>IECStepPositionShortTimestamp</t>
+        </is>
+      </c>
+      <c r="DH15" t="inlineStr">
+        <is>
+          <t>DiscreteQualityTimeTagExtended</t>
+        </is>
+      </c>
+      <c r="DO15" t="inlineStr">
+        <is>
+          <t>DiscreteQualityTimeTagExtended</t>
+        </is>
+      </c>
+      <c r="DZ15" t="inlineStr">
+        <is>
+          <t>IECBitstringShortTimestamp</t>
+        </is>
+      </c>
+      <c r="EH15" t="inlineStr">
+        <is>
+          <t>IECBitstringShortTimestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Severidade 2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SwitchStatus</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DOMInhibit</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>FUSEC</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>FaultStatus</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>FaultCurrentSub</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Hz_s</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>(UTC-06:00) Central America</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>AnalogOutputStatus</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>StateExtended</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>IECBitstringShortTimestamp</t>
+        </is>
+      </c>
+      <c r="DH16" t="inlineStr">
+        <is>
+          <t>StateSuppQualityTimeTagExtended</t>
+        </is>
+      </c>
+      <c r="DO16" t="inlineStr">
+        <is>
+          <t>StateSuppQualityTimeTagExtended</t>
+        </is>
+      </c>
+      <c r="DZ16" t="inlineStr">
+        <is>
+          <t>IECMultiBitShortTimestamp</t>
+        </is>
+      </c>
+      <c r="EH16" t="inlineStr">
+        <is>
+          <t>IECMultiBitShortTimestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Severidade 1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BREAKERC</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>RecloserLockout</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ABCN</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>FaultAngleSub</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>(UTC-06:00) Central Time (US &amp; Canada)</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>AnalogOutputEvent</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>DiscreteExtended</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>IECMultiBitShortTimestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Humidity</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CONNODE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>FanStatus</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>FaultCurrentTrans</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>(UTC-06:00) Easter Island</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>ClassObjects</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>StateSuppExtended</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>WindSpeed</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BUSNODE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>OilPumpStatus</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>FaultAngleTrans</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>kWh</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>(UTC-06:00) Guadalajara, Mexico City, Monterrey</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>RealQualityTimeTagExtended</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>FeelsLike</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>POTENTIALTR</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>HotLineTag</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>DeltaVoltage</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>MWh</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>(UTC-06:00) Saskatchewan</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>SecureDNP3Statistics</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>StateQualityTimeTagExtended</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SunshineMinutes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SURGEPROTECTOR</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>MaxOpCount</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>MaxRampUp</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>kVArh</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>(UTC-05:00) Bogota, Lima, Quito, Rio Branco</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>SecureDNP3StatisticsEvent</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>DiscreteQualityTimeTagExtended</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SkyCover</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>GNDIMPEDANCE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>HourlyOpCount</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>MaxRampDown</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>MVArh</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>(UTC-05:00) Chetumal</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>StateSuppQualityTimeTagExtended</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>DailyOpCount</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Charged</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>kVA</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>(UTC-05:00) Eastern Time (US &amp; Canada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CrossSection</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SOURCE</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>MonthlyOpCount</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>EnergyPrice</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>MVA</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>(UTC-05:00) Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Impedance</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>UnderFrequencyAlarm</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>GenerationPrice</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>(UTC-05:00) Havana</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Admittance</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SYNCMACHINE</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Forward</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>PInjectedReal</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>(UTC-05:00) Indiana (East)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ImpedancePerLength</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CURRENTTR</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>RelayTrip</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>QInjectedReal</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>dms</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>(UTC-05:00) Turks and Caicos</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AdmittancePerLength</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>INDUCTOR</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ReverseMode</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>PInjectedEq</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>sec</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>(UTC-04:00) Atlantic Time (Canada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>FAULTINDICATOR</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SourceStatus</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>QInjectedEq</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>(UTC-04:00) Caracas</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SECTION</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>CalculatedVoltage</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>hour</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>(UTC-04:00) Cuiaba</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RelativeVoltage</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>TAPCHANGER</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PowerOn</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>PMin</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>km_h</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>(UTC-04:00) Georgetown, La Paz, Manaus, San Juan</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Insolation</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>POWERTR2W</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Manageable</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>PMax</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>mph</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>(UTC-04:00) Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CurrentAngle</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>POWERTR3W</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Malfunctioning</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>QMin</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>m_s</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>(UTC-03:30) Newfoundland</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RotationSpeed</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ASIGNAL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>WeightingFactor</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>QMax</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>(UTC-03:00) Araguaina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DSIGNAL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>TemporaryFault</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>SShortCircuit</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>(UTC-03:00) Asuncion</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FailureRate</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>GROUNDNODE</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>GroupStatus</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>X1R1Ratio</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>(UTC-03:00) Brasilia</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SoilTemperature</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>REMOTEPOINT</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Custom1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>RWard</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>yd</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>(UTC-03:00) Cayenne, Fortaleza</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>OilTemperature</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>CURVE</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Custom2</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>XWard</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>mi</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>(UTC-03:00) City of Buenos Aires</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>HotSpotTemperature</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>PETERSENCOIL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Custom3</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>R1ShortCircuit</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>mm2</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>(UTC-03:00) Montevideo</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AbsoluteDateTime</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>COMPSWITCH</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Custom4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>X1ShortCircuit</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>kcmil</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>(UTC-03:00) Punta Arenas</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LatLong</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>PCELL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Custom5</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>R2ShortCircuit</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>AWG</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>(UTC-03:00) Saint Pierre and Miquelon</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>REGCTRL</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Custom6</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>X2ShortCircuit</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Ohm</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>(UTC-03:00) Salvador</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LongDistanceLength</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>CTRLLIMIT</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Custom7</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>R0ShortCircuit</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>(UTC-02:00) Coordinated Universal Time-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Precipitation</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>DAYTYPE</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Custom8</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>X0ShortCircuit</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>mS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>(UTC-02:00) Greenland</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>WindDirection</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SEASON</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Custom9</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Custom1</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>uS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>(UTC-02:00) Mid-Atlantic - Old</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ThermalPower</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>LOADRSPCHAR</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Custom10</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Custom2</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Ohm_km</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>(UTC-01:00) Azores</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Emission</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>LOADPICKUPCHAR</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Custom3</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Ohm_m</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>(UTC-01:00) Cabo Verde Is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>LOADGROUP</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Custom4</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Ohm_kft</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>(UTC) Coordinated Universal Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SECTIONALIZER</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Custom5</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Ohm_mi</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>(UTC+00:00) Dublin, Edinburgh, Lisbon, London</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>RECLSTAGE</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>S_km</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>(UTC+00:00) Monrovia, Reykjavik</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>PROTECTEQP</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>S_m</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>(UTC+00:00) Sao Tome</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>RELSTAGE</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>S_kft</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>(UTC+01:00) Casablanca</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>RTUC</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>S_mi</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>(UTC+01:00) Amsterdam, Berlin, Bern, Rome, Stockholm, Vienna</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>uS_km</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>(UTC+01:00) Belgrade, Bratislava, Budapest, Ljubljana, Prague</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SUBREGION</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>uS_m</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>(UTC+01:00) Brussels, Copenhagen, Madrid, Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>FEEDER</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>uS_kft</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>(UTC+01:00) Sarajevo, Skopje, Warsaw, Zagreb</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>FEEDEROBJECT</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>uS_mi</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>(UTC+01:00) West Central Africa</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ASYNCMACHINE</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>(UTC+02:00) Athens, Bucharest</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ASYNCMACHINEC</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>pu</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>(UTC+02:00) Beirut</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>WIREC</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>base120</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>(UTC+02:00) Cairo</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CABLEC</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>(UTC+02:00) Chisinau</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>LINEGEOMETRYC</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>W_m2</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>(UTC+02:00) Gaza, Hebron</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>WEATHERREGION</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>rpm</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>(UTC+02:00) Harare, Pretoria</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>TRANSFORMERAREA</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>(UTC+02:00) Helsinki, Kyiv, Riga, Sofia, Tallinn, Vilnius</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>CONSUMERCONTRACT</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>(UTC+02:00) Jerusalem</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>JUMPER</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>lb</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>(UTC+02:00) Juba</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>LOADBREAKSWITCH</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>perYear</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>(UTC+02:00) Kaliningrad</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>BREAKER</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>mm_h</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>(UTC+02:00) Khartoum</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>CBLTHERMMODEL</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>in_h</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>(UTC+02:00) Tripoli</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ARRAYSIGNAL</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>MBTU_h</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>(UTC+02:00) Windhoek</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>INTERLOCKINGITEM</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>kcal_h</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>(UTC+03:00) Amman</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>INTERLOCKINGSCHEME</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>kJ_h</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>(UTC+03:00) Baghdad</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>CTRLSETT</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>MJ_h</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>(UTC+03:00) Damascus</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>FEEDERSEGMENT</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>khour</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>(UTC+03:00) Istanbul</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>FUSE</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>kg_h</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>(UTC+03:00) Kuwait, Riyadh</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>DISCONNECTOR</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>g_h</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>(UTC+03:00) Minsk</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>TAGC</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>(UTC+03:00) Moscow, St. Petersburg</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>MOBILEOBJECT</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>(UTC+03:00) Nairobi</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>AORGROUP</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>(UTC+03:00) Volgograd</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>CUSTOMGROUP</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>(UTC+03:30) Tehran</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>INTSCHEDULE</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>(UTC+04:00) Abu Dhabi, Muscat</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ANNUALSCHEDULE</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>(UTC+04:00) Astrakhan, Ulyanovsk</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>LVNETWORK</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>(UTC+04:00) Baku</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>LVFEEDER</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>(UTC+04:00) Izhevsk, Samara</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>TEMPSCHEDULE</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>(UTC+04:00) Port Louis</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>CURRENTTRC</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>(UTC+04:00) Saratov</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>POTENTIALTRC</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>(UTC+04:00) Tbilisi</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>MESSAGEMAPPING</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>(UTC+04:00) Yerevan</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SEASONDAYSCH</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>(UTC+04:30) Kabul</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>CUSTOMTYPE</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>(UTC+05:00) Ashgabat, Tashkent</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>GENCONTRACT</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>(UTC+05:00) Astana</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>DISTGEN</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>(UTC+05:00) Ekaterinburg</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>PWRPLANT</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>(UTC+05:00) Islamabad, Karachi</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SRVDELIVERYPOINT</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>(UTC+05:30) Chennai, Kolkata, Mumbai, New Delhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SRVLOCATION</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>(UTC+05:30) Sri Jayawardenepura</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>BUSBAR</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>(UTC+05:45) Kathmandu</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>NOTEC</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>(UTC+06:00) Bishkek</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>DYNAMICLINERATING</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>(UTC+06:00) Dhaka</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>DYNAMICPWTRATING</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>(UTC+06:00) Omsk</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>RELSETTS</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>(UTC+06:30) Yangon (Rangoon)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>DISTRELSETTS</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>(UTC+07:00) Bangkok, Hanoi, Jakarta</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>DISTRELSTAGE</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>(UTC+07:00) Barnaul, Gorno-Altaysk</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>RELCONDITION</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>(UTC+07:00) Hovd</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>REGCTRLGROUP</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>(UTC+07:00) Krasnoyarsk</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>TRBANK</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>(UTC+07:00) Novosibirsk</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>CAPBANK</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>(UTC+07:00) Tomsk</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>PROTGROUP</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>(UTC+08:00) Beijing, Chongqing, Hong Kong, Urumqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>(UTC+08:00) Irkutsk</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>METERC</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>(UTC+08:00) Kuala Lumpur, Singapore</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>LOGICALNODE</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>(UTC+08:00) Perth</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>CUSTOMEQP</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>(UTC+08:00) Taipei</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>CUSTOMBRANCH</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>(UTC+08:00) Ulaanbaatar</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>CUSTOMSHUNT</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>(UTC+08:45) Eucla</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>CUSTOMSWITCH</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>(UTC+09:00) Chita</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>FLEXIBLELOAD</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>(UTC+09:00) Osaka, Sapporo, Tokyo</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>LIMITSET</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>(UTC+09:00) Pyongyang</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>ALARMEVENTC</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>(UTC+09:00) Seoul</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>SIGNALVALUEALARM</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>(UTC+09:00) Yakutsk</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>ANALOGALARMLIMITS</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>(UTC+09:30) Adelaide</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>ADVALMLIMITS</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>(UTC+09:30) Darwin</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>(UTC+10:00) Brisbane</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>METERCMEAS</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>(UTC+10:00) Canberra, Melbourne, Sydney</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>PHASETAPCHANGER</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>(UTC+10:00) Guam, Port Moresby</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>(UTC+10:00) Hobart</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>COUNTERIEC</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>(UTC+10:00) Vladivostok</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>AINPUTIEC</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>(UTC+10:30) Lord Howe Island</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>DINPUTIEC</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>(UTC+11:00) Bougainville Island</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>AOUTPUTIEC</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>(UTC+11:00) Chokurdakh</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>DOUTPUTIEC</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>(UTC+11:00) Magadan</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>SUBRTUIEC104</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>(UTC+11:00) Norfolk Island</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>RTUIEC104</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>(UTC+11:00) Sakhalin</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>COMMLINKIEC104</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>(UTC+11:00) Solomon Is., New Caledonia</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>COMMCHANNELIEC104</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>(UTC+12:00) Anadyr, Petropavlovsk-Kamchatsky</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>AINPUTDNP3</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>(UTC+12:00) Auckland, Wellington</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>DINPUTDNP3</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>(UTC+12:00) Coordinated Universal Time+12</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>AOUTPUTDNP3</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>(UTC+12:00) Fiji</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>DOUTPUTDNP3</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>(UTC+12:00) Petropavlovsk-Kamchatsky - Old</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>RTUDNP3</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>(UTC+12:45) Chatham Islands</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>COMMLINKDNP3</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>(UTC+13:00) Coordinated Universal Time+13</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>COMMCHANNELDNP3</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>(UTC+13:00) Nuku'alofa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>COUNTERDNP3</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>(UTC+13:00) Samoa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>REMOTEINPUTICCP</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>(UTC+14:00) Kiritimati Island</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>REMOTEOUTPUTICCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>DSTSICCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>RCCICCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>APPREFICCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>ASSOCIATIONICCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>APROCESSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>DERGROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>TERMINALSERVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>RTUIEC101</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>COMMLINKIEC101</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>COMMCHANNELIEC101</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>SERIALLINK</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>TCPIPLINK</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>CALCCONSTARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>CALCSIGNALARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>CALCPARAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>CALCULATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>CALCCODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>AINPUTADMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>DINPUTADMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>AINPUTMODBUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>DINPUTMODBUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>AOUTPUTMODBUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>DOUTPUTMODBUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>RTUMODBUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>COMMLINKMODBUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>COMMCHANNELMODBUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>MODEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>MODEMBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>MODEMLINK</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>SCANGROUPDNP3</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>NETCONFIGICCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>AINPUT2179</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>DINPUT2179</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>RPOINT2179</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>AOUTPUT2179</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>DOUTPUT2179</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>RTU2179</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>COMMLINK2179</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>COMMCHANNEL2179</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>SCANGROUP2179</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>SUBRTU2179</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>AINPUTCUSTOM1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>DINPUTCUSTOM1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>AOUTPUTCUSTOM1</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>DOUTPUTCUSTOM1</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>COMMCHANNELCUSTOM1</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>RTUCUSTOM1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>COMMLINKCUSTOM1</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>AINPUTCUSTOM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>DINPUTCUSTOM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>AOUTPUTCUSTOM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>DOUTPUTCUSTOM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>COMMCHANNELCUSTOM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>RTUCUSTOM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>COMMLINKCUSTOM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>AINPUTCUSTOM3</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>DINPUTCUSTOM3</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>AOUTPUTCUSTOM3</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>DOUTPUTCUSTOM3</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>COMMCHANNELCUSTOM3</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>RTUCUSTOM3</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>COMMLINKCUSTOM3</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>AINPUT61850</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>DINPUT61850</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>AOUTPUT61850</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>DOUTPUT61850</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>COMMCHANNEL61850</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>RTU61850</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>COMMLINK61850</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>AINPUTDNP3SLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>DINPUTDNP3SLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>AOUTPUTDNP3SLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>DOUTPUTDNP3SLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>COMMCHANNELDNP3SLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>RTUDNP3SLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>COMMLINKDNP3SLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>COUNTERDNP3SLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>AINPUTS5</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>DINPUTS5</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>AOUTPUTS5</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>DOUTPUTS5</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>RTUS5</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>COMMLINKS5</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>COMMCHANNELS5</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>SCANGROUPS5</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>CONDITIONALSCHM</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>DOMCATALOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>AINPUTMETER</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>DINPUTMETER</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>RTUVCOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>COMMLINKVCOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>COMMCHANNELVCOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>SCANGROUPVCOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>AINPUTVCOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>AOUTPUTVCOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>DINPUTVCOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>DOUTPUTVCOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>RTUMD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>COMMLINKMD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>COMMCHANNELMD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>SCANGROUPMD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>AINPUTMD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>AOUTPUTMD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>DINPUTMD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>DOUTPUTMD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>RTUCONITEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>COMMLINKCONITEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>COMMCHANNELCONITEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>SCANGROUPCONITEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>AINPUTCONITEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>AOUTPUTCONITEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>DINPUTCONITEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>DOUTPUTCONITEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>SECUREDNP3</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>TEMPLATEINSTANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>TMPMOBILEOBJECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>TMPCUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>TMPGENERATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>TMPGROUNDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>TMPJUMPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>TMPSWITCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>FAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>TMPLOAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>CHATTERPROCESSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>EVENTSCHEDULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>AINPUTIECSLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>DINPUTIECSLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>COUNTERIECSLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>AOUTPUTIECSLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>DOUTPUTIECSLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>RTUIECSLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>COMMCHANNELIEC101SLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>COMMLINKIEC101SLAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>UDPLINK</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>TLS</t>
         </is>
       </c>
     </row>
@@ -13348,10 +18264,19 @@
       <formula>LEN(TRIM(A5))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="H5:I5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and 86400." type="decimal">
+  <dataValidations count="4">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$A$2:$A$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5 M5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$B$2:$B$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="H5 I5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and 86400." type="decimal">
       <formula1>0</formula1>
       <formula2>86400</formula2>
+    </dataValidation>
+    <dataValidation sqref="J5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$C$2:$C$15</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13588,6 +18513,14 @@
       <formula>LEN(TRIM(A5))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$A$2:$A$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$E$2:$E$47</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
@@ -14017,6 +18950,11 @@
       <formula>LEN(TRIM(G5))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$A$2:$A$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
@@ -14383,6 +19321,26 @@
       <formula>AND(LEN(V5)=0,OR($P5&lt;&gt;"TapPosition"), OR($P5&lt;&gt;"OperationCount"), OR($P5&lt;&gt;"ReverseMode"), OR($P5&lt;&gt;"HourlyOpCount"), OR($P5&lt;&gt;"ControlActiveSetting"), OR($P5&lt;&gt;"DailyOpCount"), OR($P5&lt;&gt;"MonthlyOpCount"))</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="6">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$A$2:$A$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="P5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$H$2:$H$46</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$E$2:$E$47</formula1>
+    </dataValidation>
+    <dataValidation sqref="R5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$J$2:$J$17</formula1>
+    </dataValidation>
+    <dataValidation sqref="S5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$K$2:$K$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="T5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$L$2:$L$4</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
@@ -14918,7 +19876,31 @@
       <formula>LEN(TRIM(U5))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations count="11">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$A$2:$A$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="P5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$M$2:$M$49</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$E$2:$E$47</formula1>
+    </dataValidation>
+    <dataValidation sqref="R5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$N$2:$N$76</formula1>
+    </dataValidation>
+    <dataValidation sqref="S5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$J$2:$J$17</formula1>
+    </dataValidation>
+    <dataValidation sqref="T5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$K$2:$K$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="U5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$L$2:$L$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="W5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$O$2:$O$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AA5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between -1 and 100." type="decimal">
       <formula1>-1</formula1>
       <formula2>100</formula2>
@@ -15800,10 +20782,22 @@
       <formula>LEN(TRIM(AD5))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="12">
+  <dataValidations count="20">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$A$2:$A$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="I5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$CK$2:$CK$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="J5 M5 N5 R5 Z5 AB5 AE5 AF5 AG5 AJ5 AK5 AM5 AN5 AQ5 AS5 AU5 AW5 AY5 BA5 BD5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$B$2:$B$3</formula1>
+    </dataValidation>
     <dataValidation sqref="K5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and 86400." type="decimal">
       <formula1>0</formula1>
       <formula2>86400</formula2>
+    </dataValidation>
+    <dataValidation sqref="L5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$Q$2:$Q$142</formula1>
     </dataValidation>
     <dataValidation sqref="O5 P5 W5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and +∞." type="decimal">
       <formula1>0</formula1>
@@ -15817,6 +20811,9 @@
       <formula1>0.1</formula1>
       <formula2>300</formula2>
     </dataValidation>
+    <dataValidation sqref="X5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$R$2:$R$5</formula1>
+    </dataValidation>
     <dataValidation sqref="Y5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 1 and 10." type="whole">
       <formula1>1</formula1>
       <formula2>10</formula2>
@@ -15829,9 +20826,15 @@
       <formula1>0</formula1>
       <formula2>65535</formula2>
     </dataValidation>
+    <dataValidation sqref="AH5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$AE$2:$AE$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AI5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 0 and 10800." type="decimal">
       <formula1>0</formula1>
       <formula2>10800</formula2>
+    </dataValidation>
+    <dataValidation sqref="AL5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$AG$2:$AG$5</formula1>
     </dataValidation>
     <dataValidation sqref="AO5 AT5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Entry must be a number between 1 and 86400." type="decimal">
       <formula1>1</formula1>
@@ -15849,6 +20852,9 @@
       <formula1>1</formula1>
       <formula2>604800</formula2>
     </dataValidation>
+    <dataValidation sqref="BC5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="entry not valid" type="list">
+      <formula1>DMSMatchingTemplateInfo!$AF$2:$AF$3</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
